--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:52</t>
+    <t xml:space="preserve">2026-09-10 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:02</t>
+    <t xml:space="preserve">2026-09-18 11:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:09</t>
+    <t xml:space="preserve">2026-09-23 14:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:32</t>
+    <t xml:space="preserve">2026-10-02 15:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Lota</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Curanilahue</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:50</t>
+    <t xml:space="preserve">2026-10-04 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:19</t>
+    <t xml:space="preserve">2026-10-05 15:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
